--- a/docs/templates/mock_drive/2026001 — Rockland/JOBCOST/2026001_JOBCOST.xlsx
+++ b/docs/templates/mock_drive/2026001 — Rockland/JOBCOST/2026001_JOBCOST.xlsx
@@ -441,71 +441,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>JOBCOST — 2026001 Rockland</t>
+          <t>JOBCOST — 2026001 Rockland (MOCK, pilot-scale demo)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>NOT the canonical template</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Canonical job-cost ledger: actuals (Cost_Ledger) + forecast (Scope_Budget) + change orders + order quantities.</t>
+          <t>This file is a lightweight pilot-scale mock for Drive-organization and parser-shape demonstration only. The canonical, owner-built gold-standard JOBCOST workbook is docs/JOB_COST_TEMPLATE_structured.xlsx (Project_Setup, Cost_Ledger, Scope_Budget, Change_Orders, Order_Quantities, Cost_Code_Summary, Progress_Valuation, Dashboard, Lists, Parser_Contract).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Main input tables</t>
+          <t>Production rule</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tblCostLedger, tblScopeBudget, tblChangeOrders, tblOrderQuantities.</t>
+          <t>For each real project, copy JOB_COST_TEMPLATE_structured.xlsx into the project folder as {project_code}_JOBCOST.xlsx and use ITS Parser_Contract as the ingestion contract. Do not build a separate simplified JOBCOST model.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Summary logic</t>
+          <t>Purpose of this mock</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dashboard uses SUMIFS by Cost_Class, Cost_Code, and Include flags.</t>
+          <t>Demonstrate the same sheet roles at smaller scale: actuals (Cost_Ledger) + forecast (Scope_Budget) + change orders + order quantities.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Append rule</t>
+          <t>Main input tables</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Append rows inside named tables. Do not build summaries from fixed row ranges.</t>
+          <t>tblCostLedger, tblScopeBudget, tblChangeOrders, tblOrderQuantities.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>Append rule</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Append rows inside named tables. Do not build summaries from fixed row ranges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Parser rule</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Only ingest sheets listed Ingest=Y in Parser_Contract.</t>
         </is>
